--- a/results/Int Task Remove ACC 0.4/Rando_2_permute.xlsx
+++ b/results/Int Task Remove ACC 0.4/Rando_2_permute.xlsx
@@ -440,887 +440,887 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.681034147224548</v>
+        <v>0.6257740263854631</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>hrv_rms</t>
+          <t>scl_lineintegral</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.6580294630128306</v>
+        <v>0.6347704283677672</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>hrv_mean</t>
+          <t>scl_peaks</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.6547749541761897</v>
+        <v>0.6347704283677672</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>scl_n_above_mean</t>
+          <t>scl_entropy</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.655432101559141</v>
+        <v>0.7246602249326786</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>scl_perm_entropy</t>
+          <t>hrv_energy</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.6577841641963296</v>
+        <v>0.7093584666561065</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>scl_iqr</t>
+          <t>bvp_lineintegral</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.6541028716254441</v>
+        <v>0.7007114570840216</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>scl_min</t>
+          <t>scl_energy</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.6426860672987713</v>
+        <v>0.7129831866217102</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
-          <t>bvp_ptp</t>
+          <t>bvp_entropy</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.6437446538888009</v>
+        <v>0.7129831866217102</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
         <is>
-          <t>scr_lineintegral</t>
+          <t>scl_max</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.6614088841619334</v>
+        <v>0.7102088660586997</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="inlineStr">
         <is>
-          <t>scr_min</t>
+          <t>scr_entropy</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.662415423955104</v>
+        <v>0.7095413093163766</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="1" t="inlineStr">
         <is>
-          <t>scl_max</t>
+          <t>scl_kurtosis</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>0.6459405761354122</v>
+        <v>0.7135674684890589</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="1" t="inlineStr">
         <is>
-          <t>hrv_perm_entropy</t>
+          <t>bvp_sum</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>0.6459405761354122</v>
+        <v>0.7128999117467358</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
         <is>
-          <t>hrv_skewness</t>
+          <t>scl_pct_5</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>0.6486108031047045</v>
+        <v>0.6801479939354167</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="1" t="inlineStr">
         <is>
-          <t>scr_n_sign_changes</t>
+          <t>hrv_perm_entropy</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>0.6479432463623815</v>
+        <v>0.6814831074200629</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="1" t="inlineStr">
         <is>
-          <t>scr_peaks</t>
+          <t>hrv_n_below_mean</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0.6479432463623815</v>
+        <v>0.6758036704306307</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="1" t="inlineStr">
         <is>
-          <t>scr_max</t>
+          <t>scr_peaks</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>0.6485691656672172</v>
+        <v>0.6761426534814782</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="1" t="inlineStr">
         <is>
-          <t>bvp_max</t>
+          <t>scl_sum</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>0.621579959720305</v>
+        <v>0.7163580819623905</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
         <is>
-          <t>hrv_pct_95</t>
+          <t>scl_skewness</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>0.6112276255346111</v>
+        <v>0.7196854563146342</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="1" t="inlineStr">
         <is>
-          <t>scr_pct_95</t>
+          <t>bvp_n_above_mean</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>0.6071806476431852</v>
+        <v>0.6710814419225635</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="1" t="inlineStr">
         <is>
-          <t>hrv_peaks</t>
+          <t>bvp_rms</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>0.6071806476431852</v>
+        <v>0.651868027426399</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="1" t="inlineStr">
         <is>
-          <t>scr_iqr</t>
+          <t>hrv_peaks</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>0.6263628340612342</v>
+        <v>0.6508614876332285</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="1" t="inlineStr">
         <is>
-          <t>scl_n_below_mean</t>
+          <t>scl_std</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>0.6160104998755402</v>
+        <v>0.6957706320291461</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="1" t="inlineStr">
         <is>
-          <t>scl_n_sign_changes</t>
+          <t>scl_svd_entropy</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>0.6170170396687108</v>
+        <v>0.6795410830259555</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="1" t="inlineStr">
         <is>
-          <t>bvp_iqr</t>
+          <t>scr_ptp</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>0.6052775452015116</v>
+        <v>0.6767563531035732</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="1" t="inlineStr">
         <is>
-          <t>hrv_iqr_5_95</t>
+          <t>bvp_mean</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>0.6093349324523093</v>
+        <v>0.6788006607680297</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="1" t="inlineStr">
         <is>
-          <t>scl_std</t>
+          <t>bvp_ptp</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>0.6065293838111833</v>
+        <v>0.6874684890588582</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="1" t="inlineStr">
         <is>
-          <t>scr_ptp</t>
+          <t>scr_pct_95</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>0.6167776244031591</v>
+        <v>0.6675250616641397</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="1" t="inlineStr">
         <is>
-          <t>hrv_max</t>
+          <t>hrv_std</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>0.5710551922337128</v>
+        <v>0.6366821298454437</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="1" t="inlineStr">
         <is>
-          <t>bvp_kurtosis</t>
+          <t>bvp_iqr_5_95</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>0.5711488764680591</v>
+        <v>0.592211536285669</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="1" t="inlineStr">
         <is>
-          <t>bvp_lineintegral</t>
+          <t>scl_iqr_5_95</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>0.5875924962096355</v>
+        <v>0.6035704102645334</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="1" t="inlineStr">
         <is>
-          <t>bvp_min</t>
+          <t>bvp_skewness</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>0.6036971329003643</v>
+        <v>0.5940268380439456</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="1" t="inlineStr">
         <is>
-          <t>bvp_std</t>
+          <t>hrv_skewness</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>0.5953474689416397</v>
+        <v>0.5956801158606956</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="1" t="inlineStr">
         <is>
-          <t>scr_perm_entropy</t>
+          <t>scr_skewness</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>0.5856314634201534</v>
+        <v>0.5996542282365187</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="1" t="inlineStr">
         <is>
-          <t>bvp_svd_entropy</t>
+          <t>hrv_mean</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>0.5630965581226947</v>
+        <v>0.5916643660473853</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="1" t="inlineStr">
         <is>
-          <t>scl_rms</t>
+          <t>hrv_iqr_5_95</t>
         </is>
       </c>
       <c r="B36" t="n">
-        <v>0.5910923038627776</v>
+        <v>0.6039777330225612</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="1" t="inlineStr">
         <is>
-          <t>hrv_ptp</t>
+          <t>scl_iqr</t>
         </is>
       </c>
       <c r="B37" t="n">
-        <v>0.5986332058563961</v>
+        <v>0.6240727749994344</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="1" t="inlineStr">
         <is>
-          <t>scr_n_below_mean</t>
+          <t>scr_iqr_5_95</t>
         </is>
       </c>
       <c r="B38" t="n">
-        <v>0.5908782331243918</v>
+        <v>0.6344667466226155</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="1" t="inlineStr">
         <is>
-          <t>hrv_std</t>
+          <t>hrv_lineintegral</t>
         </is>
       </c>
       <c r="B39" t="n">
-        <v>0.5698762191396438</v>
+        <v>0.6518336312823878</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="1" t="inlineStr">
         <is>
-          <t>bvp_n_above_mean</t>
+          <t>bvp_pct_5</t>
         </is>
       </c>
       <c r="B40" t="n">
-        <v>0.5731796067072481</v>
+        <v>0.6024032042723632</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="1" t="inlineStr">
         <is>
-          <t>scl_mean</t>
+          <t>scr_n_below_mean</t>
         </is>
       </c>
       <c r="B41" t="n">
-        <v>0.5767196940553506</v>
+        <v>0.594762734493449</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="1" t="inlineStr">
         <is>
-          <t>bvp_pct_5</t>
+          <t>scr_n_sign_changes</t>
         </is>
       </c>
       <c r="B42" t="n">
-        <v>0.5420438550836143</v>
+        <v>0.594762734493449</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="1" t="inlineStr">
         <is>
-          <t>hrv_n_above_mean</t>
+          <t>scl_min</t>
         </is>
       </c>
       <c r="B43" t="n">
-        <v>0.5454232762327171</v>
+        <v>0.5952786766536172</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="1" t="inlineStr">
         <is>
-          <t>hrv_min</t>
+          <t>scr_svd_entropy</t>
         </is>
       </c>
       <c r="B44" t="n">
-        <v>0.5321807607883958</v>
+        <v>0.583038175194044</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="1" t="inlineStr">
         <is>
-          <t>bvp_perm_entropy</t>
+          <t>scl_pct_95</t>
         </is>
       </c>
       <c r="B45" t="n">
-        <v>0.4523817066823561</v>
+        <v>0.5729935959810821</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="1" t="inlineStr">
         <is>
-          <t>bvp_entropy</t>
+          <t>scr_sum</t>
         </is>
       </c>
       <c r="B46" t="n">
-        <v>0.4523817066823561</v>
+        <v>0.5528732094770428</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="1" t="inlineStr">
         <is>
-          <t>bvp_sum</t>
+          <t>scl_n_above_mean</t>
         </is>
       </c>
       <c r="B47" t="n">
-        <v>0.4520427236315087</v>
+        <v>0.5521744246566043</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="1" t="inlineStr">
         <is>
-          <t>hrv_iqr</t>
+          <t>hrv_min</t>
         </is>
       </c>
       <c r="B48" t="n">
-        <v>0.4447100088253264</v>
+        <v>0.5772546446108936</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="1" t="inlineStr">
         <is>
-          <t>hrv_sum</t>
+          <t>scr_min</t>
         </is>
       </c>
       <c r="B49" t="n">
-        <v>0.4760005430970107</v>
+        <v>0.576248104817723</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="1" t="inlineStr">
         <is>
-          <t>scl_entropy</t>
+          <t>hrv_n_above_mean</t>
         </is>
       </c>
       <c r="B50" t="n">
-        <v>0.4761105202416782</v>
+        <v>0.5765766785091987</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="1" t="inlineStr">
         <is>
-          <t>scr_entropy</t>
+          <t>scr_energy</t>
         </is>
       </c>
       <c r="B51" t="n">
-        <v>0.4761105202416782</v>
+        <v>0.560602837681881</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="1" t="inlineStr">
         <is>
-          <t>scl_svd_entropy</t>
+          <t>scl_n_sign_changes</t>
         </is>
       </c>
       <c r="B52" t="n">
-        <v>0.4989545382543957</v>
+        <v>0.5589495598651308</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="1" t="inlineStr">
         <is>
-          <t>bvp_energy</t>
+          <t>scl_n_below_mean</t>
         </is>
       </c>
       <c r="B53" t="n">
-        <v>0.52990156366681</v>
+        <v>0.5422502319476816</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="1" t="inlineStr">
         <is>
-          <t>hrv_entropy</t>
+          <t>bvp_iqr</t>
         </is>
       </c>
       <c r="B54" t="n">
-        <v>0.5174945124572877</v>
+        <v>0.4910814419225634</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="1" t="inlineStr">
         <is>
-          <t>scl_kurtosis</t>
+          <t>scr_perm_entropy</t>
         </is>
       </c>
       <c r="B55" t="n">
-        <v>0.5155022515896902</v>
+        <v>0.4741888619854722</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="1" t="inlineStr">
         <is>
-          <t>scl_peaks</t>
+          <t>hrv_entropy</t>
         </is>
       </c>
       <c r="B56" t="n">
-        <v>0.5155022515896902</v>
+        <v>0.4965988549704691</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="1" t="inlineStr">
         <is>
-          <t>bvp_iqr_5_95</t>
+          <t>hrv_ptp</t>
         </is>
       </c>
       <c r="B57" t="n">
-        <v>0.4993188658324093</v>
+        <v>0.461921658256206</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="1" t="inlineStr">
         <is>
-          <t>bvp_skewness</t>
+          <t>bvp_pct_95</t>
         </is>
       </c>
       <c r="B58" t="n">
-        <v>0.5299490846552466</v>
+        <v>0.4859822135728994</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="1" t="inlineStr">
         <is>
-          <t>bvp_pct_95</t>
+          <t>hrv_pct_95</t>
         </is>
       </c>
       <c r="B59" t="n">
-        <v>0.5396859088954764</v>
+        <v>0.524999207983526</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="1" t="inlineStr">
         <is>
-          <t>scr_svd_entropy</t>
+          <t>bvp_n_sign_changes</t>
         </is>
       </c>
       <c r="B60" t="n">
-        <v>0.5319250526125229</v>
+        <v>0.4772342784729923</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="1" t="inlineStr">
         <is>
-          <t>hrv_n_below_mean</t>
+          <t>bvp_min</t>
         </is>
       </c>
       <c r="B61" t="n">
-        <v>0.5249105021384445</v>
+        <v>0.530164513136159</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="1" t="inlineStr">
         <is>
-          <t>scr_rms</t>
+          <t>hrv_kurtosis</t>
         </is>
       </c>
       <c r="B62" t="n">
-        <v>0.5063497092168088</v>
+        <v>0.5371582448914938</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="1" t="inlineStr">
         <is>
-          <t>bvp_mean</t>
+          <t>hrv_svd_entropy</t>
         </is>
       </c>
       <c r="B63" t="n">
-        <v>0.5066886922676563</v>
+        <v>0.5516675341132811</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="1" t="inlineStr">
         <is>
-          <t>bvp_rms</t>
+          <t>hrv_sum</t>
         </is>
       </c>
       <c r="B64" t="n">
-        <v>0.5266796406508113</v>
+        <v>0.563295693693286</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="1" t="inlineStr">
         <is>
-          <t>scl_lineintegral</t>
+          <t>scr_mean</t>
         </is>
       </c>
       <c r="B65" t="n">
-        <v>0.5086406734402933</v>
+        <v>0.527554026838044</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="1" t="inlineStr">
         <is>
-          <t>bvp_n_below_mean</t>
+          <t>scl_ptp</t>
         </is>
       </c>
       <c r="B66" t="n">
-        <v>0.5680278789798828</v>
+        <v>0.5236287931931841</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="1" t="inlineStr">
         <is>
-          <t>scr_iqr_5_95</t>
+          <t>bvp_n_below_mean</t>
         </is>
       </c>
       <c r="B67" t="n">
-        <v>0.5542603697585481</v>
+        <v>0.6274137267769455</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="1" t="inlineStr">
         <is>
-          <t>scl_ptp</t>
+          <t>scr_max</t>
         </is>
       </c>
       <c r="B68" t="n">
-        <v>0.553505012332828</v>
+        <v>0.6184856645018216</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="1" t="inlineStr">
         <is>
-          <t>hrv_kurtosis</t>
+          <t>bvp_peaks</t>
         </is>
       </c>
       <c r="B69" t="n">
-        <v>0.5520078749066553</v>
+        <v>0.5358158901133715</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="1" t="inlineStr">
         <is>
-          <t>scr_kurtosis</t>
+          <t>scl_rms</t>
         </is>
       </c>
       <c r="B70" t="n">
-        <v>0.5385481206580525</v>
+        <v>0.5359466859767825</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="1" t="inlineStr">
         <is>
-          <t>scl_pct_5</t>
+          <t>bvp_energy</t>
         </is>
       </c>
       <c r="B71" t="n">
-        <v>0.5471892466791881</v>
+        <v>0.5531782489647213</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="1" t="inlineStr">
         <is>
-          <t>scl_iqr_5_95</t>
+          <t>scr_pct_5</t>
         </is>
       </c>
       <c r="B72" t="n">
-        <v>0.5503116019098911</v>
+        <v>0.5551496911135751</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="1" t="inlineStr">
         <is>
-          <t>scr_std</t>
+          <t>bvp_svd_entropy</t>
         </is>
       </c>
       <c r="B73" t="n">
-        <v>0.541200696974497</v>
+        <v>0.5969781177162771</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="1" t="inlineStr">
         <is>
-          <t>hrv_pct_5</t>
+          <t>scl_perm_entropy</t>
         </is>
       </c>
       <c r="B74" t="n">
-        <v>0.5699205720621846</v>
+        <v>0.596310560973954</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="1" t="inlineStr">
         <is>
-          <t>bvp_n_sign_changes</t>
+          <t>bvp_perm_entropy</t>
         </is>
       </c>
       <c r="B75" t="n">
-        <v>0.5179955194496617</v>
+        <v>0.5038428639315697</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="1" t="inlineStr">
         <is>
-          <t>scr_sum</t>
+          <t>scr_n_above_mean</t>
         </is>
       </c>
       <c r="B76" t="n">
-        <v>0.51674368083999</v>
+        <v>0.498810164965717</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" s="1" t="inlineStr">
         <is>
-          <t>scl_pct_95</t>
+          <t>scl_mean</t>
         </is>
       </c>
       <c r="B77" t="n">
-        <v>0.5173279627073386</v>
+        <v>0.5369473422190039</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="1" t="inlineStr">
         <is>
-          <t>scr_mean</t>
+          <t>bvp_max</t>
         </is>
       </c>
       <c r="B78" t="n">
-        <v>0.5402624968885067</v>
+        <v>0.5930533366522595</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="1" t="inlineStr">
         <is>
-          <t>hrv_energy</t>
+          <t>hrv_iqr</t>
         </is>
       </c>
       <c r="B79" t="n">
-        <v>0.5417433414043583</v>
+        <v>0.5919010658278835</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="1" t="inlineStr">
         <is>
-          <t>scr_energy</t>
+          <t>hrv_n_sign_changes</t>
         </is>
       </c>
       <c r="B80" t="n">
-        <v>0.5179389468443801</v>
+        <v>0.5919010658278835</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" s="1" t="inlineStr">
         <is>
-          <t>bvp_peaks</t>
+          <t>hrv_max</t>
         </is>
       </c>
       <c r="B81" t="n">
-        <v>0.5101930257292209</v>
+        <v>0.5299314340023987</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" s="1" t="inlineStr">
         <is>
-          <t>scr_n_above_mean</t>
+          <t>hrv_rms</t>
         </is>
       </c>
       <c r="B82" t="n">
-        <v>0.5036274354506574</v>
+        <v>0.5273607748184019</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" s="1" t="inlineStr">
         <is>
-          <t>scr_pct_5</t>
+          <t>scr_rms</t>
         </is>
       </c>
       <c r="B83" t="n">
-        <v>0.5055156027245367</v>
+        <v>0.5259365029078319</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" s="1" t="inlineStr">
         <is>
-          <t>hrv_svd_entropy</t>
+          <t>bvp_kurtosis</t>
         </is>
       </c>
       <c r="B84" t="n">
-        <v>0.4930981421556425</v>
+        <v>0.5361951528591794</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" s="1" t="inlineStr">
         <is>
-          <t>scr_skewness</t>
+          <t>hrv_pct_5</t>
         </is>
       </c>
       <c r="B85" t="n">
-        <v>0.4972596230001584</v>
+        <v>0.5156525084293182</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" s="1" t="inlineStr">
         <is>
-          <t>hrv_lineintegral</t>
+          <t>scr_std</t>
         </is>
       </c>
       <c r="B86" t="n">
-        <v>0.482452988165011</v>
+        <v>0.5318716480731371</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" s="1" t="inlineStr">
         <is>
-          <t>scl_energy</t>
+          <t>bvp_std</t>
         </is>
       </c>
       <c r="B87" t="n">
-        <v>0.4824113507275237</v>
+        <v>0.5476744133420832</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" s="1" t="inlineStr">
         <is>
-          <t>hrv_n_sign_changes</t>
+          <t>scr_iqr</t>
         </is>
       </c>
       <c r="B88" t="n">
-        <v>0.4824113507275237</v>
+        <v>0.5573800095041976</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" s="1" t="inlineStr">
         <is>
-          <t>scl_skewness</t>
+          <t>scr_lineintegral</t>
         </is>
       </c>
       <c r="B89" t="n">
-        <v>0.4796162114457695</v>
+        <v>0.4935900975311716</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" s="1" t="inlineStr">
         <is>
-          <t>scl_sum</t>
+          <t>scr_kurtosis</t>
         </is>
       </c>
       <c r="B90" t="n">
-        <v>0.5012025072978661</v>
+        <v>0.4904663845579417</v>
       </c>
     </row>
   </sheetData>
